--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcfad0d7b95a84879"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R76202792ab40476e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R76202792ab40476e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83fd6348b2634372"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83fd6348b2634372"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd716714f1f884982"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd716714f1f884982"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca7f0783481249ea"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca7f0783481249ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra270e9feb0a047a1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra270e9feb0a047a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26422c0eff4a4da3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26422c0eff4a4da3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2a02143f6b694b82"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2a02143f6b694b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6bc96c99ff74de8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6bc96c99ff74de8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6e6409e65a6549c0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6e6409e65a6549c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd8be09fde1864795"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd8be09fde1864795"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbeff4f95eeac4e15"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbeff4f95eeac4e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8279ebe5d6c146fe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8279ebe5d6c146fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd547990ad0f4ee4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd547990ad0f4ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc0d7cd295dcd4fe2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc0d7cd295dcd4fe2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd6fd4daef774b11"/>
   </x:sheets>
 </x:workbook>
 </file>
